--- a/DMW/other-forms/PURCHASE ORDERS.xlsx
+++ b/DMW/other-forms/PURCHASE ORDERS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kurt\Desktop\PROCUREMENT SYSTEM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kurt\Desktop\PROCUREMENT SYSTEM\DMW_System\DMW\other-forms\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{606C3490-5CC7-4C61-A493-B7A75611656B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F335A9F6-1E57-4CD2-B269-4F113617B380}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{81729B17-A229-474C-802D-E02BBF805346}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -35,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1804" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1804" uniqueCount="237">
   <si>
     <t>UID</t>
   </si>
@@ -743,6 +742,9 @@
   </si>
   <si>
     <t>Procurement of cellphone for the DMW Division's Hotline</t>
+  </si>
+  <si>
+    <t>placeOfDelivery</t>
   </si>
 </sst>
 </file>
@@ -804,7 +806,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -816,9 +818,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1210,7 +1209,7 @@
         <v>28</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>22</v>
+        <v>236</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>29</v>
@@ -6157,7 +6156,7 @@
       <c r="E77" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F77" s="5" t="s">
+      <c r="F77" s="1" t="s">
         <v>158</v>
       </c>
       <c r="G77" s="1" t="s">
